--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ ЗПФ/дв 16,07,26 бррсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ ЗПФ/дв 16,07,26 бррсч пок зпф.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D192373F-D136-4028-8A19-A141AA8E6F6C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E21E7C-1043-4F85-83C0-50F6E2350DF4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="176">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -556,6 +556,9 @@
   </si>
   <si>
     <t>СЕТИ</t>
+  </si>
+  <si>
+    <t>нет</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1329,9 @@
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="7"/>
-      <c r="AH4" s="9"/>
+      <c r="AH4" s="9" t="s">
+        <v>175</v>
+      </c>
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
